--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.51863</v>
+        <v>17.25736</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30391</v>
+        <v>17.08969</v>
       </c>
       <c r="E2" t="n">
-        <v>16.85153</v>
+        <v>17.1953</v>
       </c>
       <c r="F2" t="n">
-        <v>43.68888</v>
+        <v>43.4555</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05113</v>
+        <v>0.05141</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82345</v>
+        <v>1.90089</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.45859</v>
+        <v>17.4441</v>
       </c>
       <c r="D3" t="n">
-        <v>17.14021</v>
+        <v>17.14577</v>
       </c>
       <c r="E3" t="n">
-        <v>17.59562</v>
+        <v>17.32766</v>
       </c>
       <c r="F3" t="n">
-        <v>43.91426</v>
+        <v>43.60711</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0523</v>
+        <v>0.05292</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89949</v>
+        <v>1.86816</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96049</v>
+        <v>17.38258</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8658</v>
+        <v>17.07742</v>
       </c>
       <c r="E4" t="n">
-        <v>17.17799</v>
+        <v>17.21336</v>
       </c>
       <c r="F4" t="n">
-        <v>43.97373</v>
+        <v>42.84829</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05242</v>
+        <v>0.0514</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8504</v>
+        <v>1.88886</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.50658</v>
+        <v>17.3434</v>
       </c>
       <c r="D5" t="n">
-        <v>17.0565</v>
+        <v>17.18065</v>
       </c>
       <c r="E5" t="n">
-        <v>17.0435</v>
+        <v>17.24871</v>
       </c>
       <c r="F5" t="n">
-        <v>44.49975</v>
+        <v>44.30436</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05171</v>
+        <v>0.05265</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92713</v>
+        <v>1.86873</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>17.25354</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17.00878</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.14518</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42.7255</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.84887</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.21583</v>
+        <v>17.39528</v>
       </c>
       <c r="D7" t="n">
-        <v>16.85953</v>
+        <v>17.06765</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2274</v>
+        <v>17.12488</v>
       </c>
       <c r="F7" t="n">
-        <v>44.55983</v>
+        <v>43.70581</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05199</v>
+        <v>0.05227</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92277</v>
+        <v>1.84171</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.32361</v>
+        <v>17.47035</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87913</v>
+        <v>17.09755</v>
       </c>
       <c r="E8" t="n">
-        <v>17.17218</v>
+        <v>17.31224</v>
       </c>
       <c r="F8" t="n">
-        <v>43.85749</v>
+        <v>44.18047</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05257</v>
+        <v>0.05294</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90656</v>
+        <v>1.91104</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.3745</v>
+        <v>17.44501</v>
       </c>
       <c r="D9" t="n">
-        <v>17.03973</v>
+        <v>16.87186</v>
       </c>
       <c r="E9" t="n">
-        <v>16.95443</v>
+        <v>17.13473</v>
       </c>
       <c r="F9" t="n">
-        <v>44.00527</v>
+        <v>43.11574</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05199</v>
+        <v>0.05247</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87305</v>
+        <v>1.91926</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.42955</v>
+        <v>17.44733</v>
       </c>
       <c r="D10" t="n">
-        <v>16.84397</v>
+        <v>17.21411</v>
       </c>
       <c r="E10" t="n">
-        <v>17.12063</v>
+        <v>17.27998</v>
       </c>
       <c r="F10" t="n">
-        <v>43.51364</v>
+        <v>45.07268</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05203</v>
+        <v>0.05194</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84801</v>
+        <v>1.87796</v>
       </c>
     </row>
     <row r="11">
@@ -683,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.89874</v>
+        <v>17.50603</v>
       </c>
       <c r="D12" t="n">
-        <v>16.28025</v>
+        <v>16.72357</v>
       </c>
       <c r="E12" t="n">
-        <v>16.69457</v>
+        <v>16.88155</v>
       </c>
       <c r="F12" t="n">
-        <v>22.30538</v>
+        <v>43.60592</v>
       </c>
       <c r="G12" t="n">
-        <v>35.23676</v>
+        <v>0.05212</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.86179</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.41279</v>
+        <v>17.39816</v>
       </c>
       <c r="D13" t="n">
-        <v>16.69598</v>
+        <v>16.75833</v>
       </c>
       <c r="E13" t="n">
-        <v>16.8924</v>
+        <v>17.3469</v>
       </c>
       <c r="F13" t="n">
-        <v>22.74435</v>
+        <v>44.83918</v>
       </c>
       <c r="G13" t="n">
-        <v>35.54951</v>
+        <v>0.05205</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.87709</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +771,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.93806</v>
+        <v>17.27194</v>
       </c>
       <c r="D14" t="n">
-        <v>16.20976</v>
+        <v>16.84984</v>
       </c>
       <c r="E14" t="n">
-        <v>16.80565</v>
+        <v>17.19075</v>
       </c>
       <c r="F14" t="n">
-        <v>22.18644</v>
+        <v>43.87854</v>
       </c>
       <c r="G14" t="n">
-        <v>34.43042</v>
+        <v>0.05143</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.89888</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.53235</v>
+        <v>17.46441</v>
       </c>
       <c r="D15" t="n">
-        <v>16.36007</v>
+        <v>16.91158</v>
       </c>
       <c r="E15" t="n">
-        <v>16.98931</v>
+        <v>17.02867</v>
       </c>
       <c r="F15" t="n">
-        <v>22.72849</v>
+        <v>44.11407</v>
       </c>
       <c r="G15" t="n">
-        <v>35.33857</v>
+        <v>0.05204</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.87397</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.15336</v>
+        <v>17.43268</v>
       </c>
       <c r="D16" t="n">
-        <v>16.47422</v>
+        <v>17.19673</v>
       </c>
       <c r="E16" t="n">
-        <v>16.85861</v>
+        <v>17.39448</v>
       </c>
       <c r="F16" t="n">
-        <v>22.02763</v>
+        <v>44.46532</v>
       </c>
       <c r="G16" t="n">
-        <v>35.17567</v>
+        <v>0.05267</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.8592</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.18378</v>
+        <v>17.23482</v>
       </c>
       <c r="D17" t="n">
-        <v>16.46701</v>
+        <v>16.8866</v>
       </c>
       <c r="E17" t="n">
-        <v>16.83033</v>
+        <v>17.06322</v>
       </c>
       <c r="F17" t="n">
-        <v>22.3107</v>
+        <v>43.57305</v>
       </c>
       <c r="G17" t="n">
-        <v>34.46142</v>
+        <v>0.05171</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.88491</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.98541</v>
+        <v>17.39842</v>
       </c>
       <c r="D18" t="n">
-        <v>16.36772</v>
+        <v>17.25412</v>
       </c>
       <c r="E18" t="n">
-        <v>17.13841</v>
+        <v>17.28762</v>
       </c>
       <c r="F18" t="n">
-        <v>21.99632</v>
+        <v>43.42484</v>
       </c>
       <c r="G18" t="n">
-        <v>34.08089</v>
+        <v>0.05153</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.89886</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.33738</v>
+        <v>17.51907</v>
       </c>
       <c r="D19" t="n">
-        <v>16.60124</v>
+        <v>17.01428</v>
       </c>
       <c r="E19" t="n">
-        <v>16.92102</v>
+        <v>17.11279</v>
       </c>
       <c r="F19" t="n">
-        <v>21.97699</v>
+        <v>43.28744</v>
       </c>
       <c r="G19" t="n">
-        <v>35.90029</v>
+        <v>0.05217</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.88423</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +922,782 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.34937</v>
+        <v>17.14566</v>
       </c>
       <c r="D20" t="n">
-        <v>16.42679</v>
+        <v>16.93307</v>
       </c>
       <c r="E20" t="n">
-        <v>16.9118</v>
+        <v>17.09661</v>
       </c>
       <c r="F20" t="n">
-        <v>22.35973</v>
+        <v>44.61553</v>
       </c>
       <c r="G20" t="n">
-        <v>34.97229</v>
+        <v>0.05283</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.86713</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.36716</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.94856</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.05367</v>
+      </c>
+      <c r="F22" t="n">
+        <v>263.28039</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16.43004</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.94716</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.17855</v>
+      </c>
+      <c r="F23" t="n">
+        <v>259.82179</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16.0953</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.00592</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.09405</v>
+      </c>
+      <c r="F24" t="n">
+        <v>257.64272</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16.33071</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.92093</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.11272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>257.85293</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16.08294</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.72892</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.88251</v>
+      </c>
+      <c r="F26" t="n">
+        <v>259.05268</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16.42684</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.9905</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.131</v>
+      </c>
+      <c r="F27" t="n">
+        <v>265.56831</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16.24064</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.09691</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.20847</v>
+      </c>
+      <c r="F28" t="n">
+        <v>260.69113</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16.05148</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.00774</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.04114</v>
+      </c>
+      <c r="F29" t="n">
+        <v>265.12378</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.23221</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.70777</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.14715</v>
+      </c>
+      <c r="F30" t="n">
+        <v>264.42774</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.52666</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.39081</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.95148</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.64743</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35.66404</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.17373</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.64367</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.05686</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.73896</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.65331</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.19088</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.68811</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.72766</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.42931</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35.56082</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.58383</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.33437</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.05443</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.46615</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.61609</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.15627</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.26861</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.66758</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.43062</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.55769</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.24933</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.46357</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.20444</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.28525</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.76911</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.13885</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.55905</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17.08974</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.80657</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.60479</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.80374</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.71765</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.72338</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.86655</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.49355</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.59544</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.13231</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.81499</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.57408</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.08317</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.14836</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.61987</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.15087</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.64014</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.15063</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.61477</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.1486</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.13005</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.62035</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.13604</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6376500000000001</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.13393</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.62943</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.15146</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.60868</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.14544</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.49672</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.94545</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17.21789</v>
+      </c>
+      <c r="F52" t="n">
+        <v>44.32969</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.36331</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17.30659</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17.35932</v>
+      </c>
+      <c r="F53" t="n">
+        <v>44.32864</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.28012</v>
+      </c>
+      <c r="D54" t="n">
+        <v>17.05905</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17.23239</v>
+      </c>
+      <c r="F54" t="n">
+        <v>43.8878</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.08029</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.83549</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.87922</v>
+      </c>
+      <c r="F55" t="n">
+        <v>44.70623</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.81528</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.93891</v>
+      </c>
+      <c r="E56" t="n">
+        <v>17.61937</v>
+      </c>
+      <c r="F56" t="n">
+        <v>43.58574</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.21788</v>
+      </c>
+      <c r="D57" t="n">
+        <v>17.09086</v>
+      </c>
+      <c r="E57" t="n">
+        <v>17.19862</v>
+      </c>
+      <c r="F57" t="n">
+        <v>44.01651</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.17482</v>
+      </c>
+      <c r="D58" t="n">
+        <v>17.1282</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17.15186</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43.18812</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.48059</v>
+      </c>
+      <c r="D59" t="n">
+        <v>17.0043</v>
+      </c>
+      <c r="E59" t="n">
+        <v>17.27704</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42.83467</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.51792</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.92654</v>
+      </c>
+      <c r="E60" t="n">
+        <v>17.34728</v>
+      </c>
+      <c r="F60" t="n">
+        <v>43.77996</v>
       </c>
     </row>
   </sheetData>
